--- a/public/data/中国公司作息情况.example.v2.xlsx
+++ b/public/data/中国公司作息情况.example.v2.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="company_schedule" sheetId="1" r:id="rId1"/>
+    <sheet name="recruit_detail" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -854,4 +855,203 @@
     <ignoredError numberStoredAsText="1" sqref="A1:N19"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>公司</v>
+      </c>
+      <c r="B1" t="str">
+        <v>城市</v>
+      </c>
+      <c r="C1" t="str">
+        <v>部门</v>
+      </c>
+      <c r="D1" t="str">
+        <v>岗位</v>
+      </c>
+      <c r="E1" t="str">
+        <v>工作制度</v>
+      </c>
+      <c r="F1" t="str">
+        <v>周末类型</v>
+      </c>
+      <c r="G1" t="str">
+        <v>上班时间</v>
+      </c>
+      <c r="H1" t="str">
+        <v>下班时间</v>
+      </c>
+      <c r="I1" t="str">
+        <v>一周工作天数</v>
+      </c>
+      <c r="J1" t="str">
+        <v>规则</v>
+      </c>
+      <c r="K1" t="str">
+        <v>证据</v>
+      </c>
+      <c r="L1" t="str">
+        <v>来源平台</v>
+      </c>
+      <c r="M1" t="str">
+        <v>来源链接</v>
+      </c>
+      <c r="N1" t="str">
+        <v>可信度</v>
+      </c>
+      <c r="O1" t="str">
+        <v>采集时间</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>示例双休科技有限公司</v>
+      </c>
+      <c r="B2" t="str">
+        <v>杭州</v>
+      </c>
+      <c r="C2" t="str">
+        <v>研发中心</v>
+      </c>
+      <c r="D2" t="str">
+        <v>后端工程师</v>
+      </c>
+      <c r="E2" t="str">
+        <v>955</v>
+      </c>
+      <c r="F2" t="str">
+        <v>双休</v>
+      </c>
+      <c r="G2" t="str">
+        <v>09:30</v>
+      </c>
+      <c r="H2" t="str">
+        <v>18:30</v>
+      </c>
+      <c r="I2" t="str">
+        <v>5</v>
+      </c>
+      <c r="J2" t="str">
+        <v>弹性工作不打卡</v>
+      </c>
+      <c r="K2" t="str">
+        <v>官网招聘页注明双休</v>
+      </c>
+      <c r="L2" t="str">
+        <v>BOSS直聘</v>
+      </c>
+      <c r="M2" t="str">
+        <v>https://www.zhipin.com/job_detail/example1.html</v>
+      </c>
+      <c r="N2" t="str">
+        <v>B</v>
+      </c>
+      <c r="O2" t="str">
+        <v>2026-06-27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>示例大小周网络有限公司</v>
+      </c>
+      <c r="B3" t="str">
+        <v>北京</v>
+      </c>
+      <c r="C3" t="str">
+        <v>增长部</v>
+      </c>
+      <c r="D3" t="str">
+        <v>前端工程师</v>
+      </c>
+      <c r="E3" t="str">
+        <v>996</v>
+      </c>
+      <c r="F3" t="str">
+        <v>大小周</v>
+      </c>
+      <c r="G3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="H3" t="str">
+        <v>21:00</v>
+      </c>
+      <c r="I3" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="J3" t="str">
+        <v>大小周, 周六轮班</v>
+      </c>
+      <c r="K3" t="str">
+        <v>职位页注明大小周</v>
+      </c>
+      <c r="L3" t="str">
+        <v>51job</v>
+      </c>
+      <c r="M3" t="str">
+        <v>https://jobs.51job.com/example2.html</v>
+      </c>
+      <c r="N3" t="str">
+        <v>B</v>
+      </c>
+      <c r="O3" t="str">
+        <v>2026-06-27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>示例单休制造有限公司</v>
+      </c>
+      <c r="B4" t="str">
+        <v>东莞</v>
+      </c>
+      <c r="C4" t="str">
+        <v>生产管理</v>
+      </c>
+      <c r="D4" t="str">
+        <v>工艺工程师</v>
+      </c>
+      <c r="E4" t="str">
+        <v>单休</v>
+      </c>
+      <c r="F4" t="str">
+        <v>单休</v>
+      </c>
+      <c r="G4" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="H4" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="I4" t="str">
+        <v>6</v>
+      </c>
+      <c r="J4" t="str">
+        <v>单休, 月休4天</v>
+      </c>
+      <c r="K4" t="str">
+        <v>招聘页明确单休</v>
+      </c>
+      <c r="L4" t="str">
+        <v>智联招聘</v>
+      </c>
+      <c r="M4" t="str">
+        <v>https://www.zhaopin.com/example3.html</v>
+      </c>
+      <c r="N4" t="str">
+        <v>C</v>
+      </c>
+      <c r="O4" t="str">
+        <v>2026-06-27</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/data/中国公司作息情况.example.v2.xlsx
+++ b/public/data/中国公司作息情况.example.v2.xlsx
@@ -859,7 +859,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -907,6 +907,9 @@
       <c r="O1" t="str">
         <v>采集时间</v>
       </c>
+      <c r="P1" t="str">
+        <v>品牌/产品</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -954,6 +957,9 @@
       <c r="O2" t="str">
         <v>2026-06-27</v>
       </c>
+      <c r="P2" t="str">
+        <v>某双休App|某云服务</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1001,6 +1007,9 @@
       <c r="O3" t="str">
         <v>2026-06-27</v>
       </c>
+      <c r="P3" t="str">
+        <v>某社交App</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1048,10 +1057,13 @@
       <c r="O4" t="str">
         <v>2026-06-27</v>
       </c>
+      <c r="P4" t="str">
+        <v>某家电品牌|某五金工具</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>